--- a/data/main/sheets/batch_05.xlsx
+++ b/data/main/sheets/batch_05.xlsx
@@ -467,18 +467,18 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_141</t>
+          <t xml:space="preserve">simple_python_230</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get current Gold price per ounce.</t>
+          <t xml:space="preserve">Who was the King of France in 1510?</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">metal = Gold
-measure = ounce</t>
+          <t xml:space="preserve">location = France
+date = 1510</t>
         </is>
       </c>
       <c r="D3" s="6"/>
@@ -490,18 +490,18 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_70</t>
+          <t xml:space="preserve">multiple_131</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who were the kings of France during the 18th century?</t>
+          <t xml:space="preserve">Find the market performance of the S&amp;P 500 and the Dow Jones over the past 5 days.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">country = France
-century = 18</t>
+          <t xml:space="preserve">indexes = S&amp;P 500, Dow Jones
+days = 5</t>
         </is>
       </c>
       <c r="D4" s="6"/>
@@ -513,19 +513,18 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_202</t>
+          <t xml:space="preserve">simple_python_181</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many greenhouse gas emissions would I save if I switched to renewable energy sources for 3 months in California?</t>
+          <t xml:space="preserve">Get details of a lawsuit with case number '123456-ABC' filed in Los Angeles court with verdict</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">energy_type = renewable
-usage_duration = 3
-region = California</t>
+          <t xml:space="preserve">case_number = 123456-ABC
+court_location = Los Angeles</t>
         </is>
       </c>
       <c r="D5" s="6"/>
@@ -537,19 +536,19 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_137</t>
+          <t xml:space="preserve">multiple_66</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search for ongoing lawsuits related to the company 'Google' filed after January 1, 2021 in California.</t>
+          <t xml:space="preserve">How much traffic should I expect from Las Vegas to Los Angeles this weekend?</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">company = Google
-start_date = January 1, 2021
-location = California</t>
+          <t xml:space="preserve">start_location = Las Vegas
+end_location = Los Angeles
+time_period = weekend</t>
         </is>
       </c>
       <c r="D6" s="6"/>
@@ -561,18 +560,19 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_379</t>
+          <t xml:space="preserve">simple_python_348</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the current time in Sydney, Australia?</t>
+          <t xml:space="preserve">Create a new player profile for the game with name 'StarPlayer' and character class 'Mage', set the starting level to 5.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Sydney
-country = Australia</t>
+          <t xml:space="preserve">player_name = StarPlayer
+_class = Mage
+starting_level = 5</t>
         </is>
       </c>
       <c r="D7" s="6"/>
@@ -584,18 +584,18 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_88</t>
+          <t xml:space="preserve">multiple_194</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me the number of active players in the game 'World of Warcraft' in 2020.</t>
+          <t xml:space="preserve">What are the opening hours of the Metropolitan Museum of Art on Saturday?</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game_title = World of Warcraft
-year = 2020</t>
+          <t xml:space="preserve">museum_name = Metropolitan Museum of Art
+day = Saturday</t>
         </is>
       </c>
       <c r="D8" s="6"/>
@@ -607,19 +607,18 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_268</t>
+          <t xml:space="preserve">simple_python_353</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me the sculptures of Michelangelo with material Marble in Rome, Italy.</t>
+          <t xml:space="preserve">What are some gluten-free recipes for dinner?</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">artist = Michelangelo
-material = Marble
-location = Rome, Italy</t>
+          <t xml:space="preserve">diet = gluten-free
+meal_type = dinner</t>
         </is>
       </c>
       <c r="D9" s="6"/>
@@ -631,18 +630,19 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_230</t>
+          <t xml:space="preserve">simple_python_67</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who was the King of France in 1510?</t>
+          <t xml:space="preserve">Identify a small green bird in forest.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = France
-date = 1510</t>
+          <t xml:space="preserve">color = green
+habitat = forest
+size = small</t>
         </is>
       </c>
       <c r="D10" s="6"/>
@@ -654,18 +654,18 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_131</t>
+          <t xml:space="preserve">simple_python_312</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the market performance of the S&amp;P 500 and the Dow Jones over the past 5 days.</t>
+          <t xml:space="preserve">What are the statistics of Ronaldo's matches in 2021?</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">indexes = S&amp;P 500, Dow Jones
-days = 5</t>
+          <t xml:space="preserve">player_name = Ronaldo
+year = 2021</t>
         </is>
       </c>
       <c r="D11" s="6"/>
@@ -677,18 +677,18 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_181</t>
+          <t xml:space="preserve">multiple_58</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get details of a lawsuit with case number '123456-ABC' filed in Los Angeles court with verdict</t>
+          <t xml:space="preserve">Search for divorce law specialists in Los Angeles</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">case_number = 123456-ABC
-court_location = Los Angeles</t>
+          <t xml:space="preserve">location = Los Angeles
+expertise = divorce</t>
         </is>
       </c>
       <c r="D12" s="6"/>
@@ -700,19 +700,20 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_66</t>
+          <t xml:space="preserve">simple_python_34</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How much traffic should I expect from Las Vegas to Los Angeles this weekend?</t>
+          <t xml:space="preserve">Create an itinerary for a 7 days trip to Tokyo with daily budgets not exceeding $100 and prefer exploring nature.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_location = Las Vegas
-end_location = Los Angeles
-time_period = weekend</t>
+          <t xml:space="preserve">destination = Tokyo
+days = 7
+daily_budget = 100
+exploration_type = nature</t>
         </is>
       </c>
       <c r="D13" s="6"/>
@@ -724,19 +725,18 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_348</t>
+          <t xml:space="preserve">simple_python_70</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create a new player profile for the game with name 'StarPlayer' and character class 'Mage', set the starting level to 5.</t>
+          <t xml:space="preserve">What is the carbon footprint of a gas-powered vehicle driving 1500 miles in a year?</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">player_name = StarPlayer
-_class = Mage
-starting_level = 5</t>
+          <t xml:space="preserve">vehicle_type = gas
+miles_driven = 1500</t>
         </is>
       </c>
       <c r="D14" s="6"/>
@@ -748,18 +748,18 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_194</t>
+          <t xml:space="preserve">multiple_163</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the opening hours of the Metropolitan Museum of Art on Saturday?</t>
+          <t xml:space="preserve">Get the list of top 5 popular artworks at the Metropolitan Museum of Art. Please sort by popularity.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">museum_name = Metropolitan Museum of Art
-day = Saturday</t>
+          <t xml:space="preserve">number = 5
+sort_by = popularity</t>
         </is>
       </c>
       <c r="D15" s="6"/>
@@ -771,18 +771,18 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_353</t>
+          <t xml:space="preserve">simple_python_183</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are some gluten-free recipes for dinner?</t>
+          <t xml:space="preserve">Search for current lawsuits filed against Apple in Santa Clara County.</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">diet = gluten-free
-meal_type = dinner</t>
+          <t xml:space="preserve">entity = Apple
+county = Santa Clara County</t>
         </is>
       </c>
       <c r="D16" s="6"/>
@@ -794,19 +794,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_67</t>
+          <t xml:space="preserve">multiple_138</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identify a small green bird in forest.</t>
+          <t xml:space="preserve">How to obtain the detailed case information of the R vs Adams legal case?</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">color = green
-habitat = forest
-size = small</t>
+          <t xml:space="preserve">case_id = R vs Adams</t>
         </is>
       </c>
       <c r="D17" s="6"/>
@@ -818,17 +816,18 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_196</t>
+          <t xml:space="preserve">simple_python_177</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the names of proteins found in the plasma membrane?</t>
+          <t xml:space="preserve">Find all Patent lawsuit cases of Facebook in 2018.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cell_compartment = plasma membrane</t>
+          <t xml:space="preserve">company_name = Facebook
+year = 2018</t>
         </is>
       </c>
       <c r="D18" s="6"/>
@@ -840,18 +839,18 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_312</t>
+          <t xml:space="preserve">simple_python_325</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the statistics of Ronaldo's matches in 2021?</t>
+          <t xml:space="preserve">Who won the last match between Chicago Bulls and Los Angeles Lakers?</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">player_name = Ronaldo
-year = 2021</t>
+          <t xml:space="preserve">team1 = Chicago Bulls
+team2 = Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D19" s="6"/>
@@ -863,18 +862,20 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_58</t>
+          <t xml:space="preserve">simple_python_385</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search for divorce law specialists in Los Angeles</t>
+          <t xml:space="preserve">Book a hotel room with king size bed in Los Angeles for 2 nights starting from 15th October,2023.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">location = Los Angeles
-expertise = divorce</t>
+room_type = king size
+check_in_date = 15th October
+no_of_nights = 2</t>
         </is>
       </c>
       <c r="D20" s="6"/>
@@ -886,19 +887,18 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_283</t>
+          <t xml:space="preserve">multiple_44</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the price of a used Gibson Les Paul guitar in excellent condition in the Chicago area.</t>
+          <t xml:space="preserve">How much will I weigh on Mars if my weight on Earth is 70 kg?</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">model = Gibson Les Paul
-condition = excellent
-location = Chicago</t>
+          <t xml:space="preserve">weight_earth_kg = 70
+planet = Mars</t>
         </is>
       </c>
       <c r="D21" s="6"/>
@@ -910,18 +910,18 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_70</t>
+          <t xml:space="preserve">simple_python_63</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the carbon footprint of a gas-powered vehicle driving 1500 miles in a year?</t>
+          <t xml:space="preserve">Find out how genetically similar a human and a chimp are in percentage.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vehicle_type = gas
-miles_driven = 1500</t>
+          <t xml:space="preserve">species1 = human
+species2 = chimp</t>
         </is>
       </c>
       <c r="D22" s="6"/>
@@ -933,18 +933,19 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_163</t>
+          <t xml:space="preserve">multiple_176</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the list of top 5 popular artworks at the Metropolitan Museum of Art. Please sort by popularity.</t>
+          <t xml:space="preserve">Give me the schedule of Manchester United for the next 6 games in Premier League.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">number = 5
-sort_by = popularity</t>
+          <t xml:space="preserve">team_name = Manchester United
+num_of_games = 6
+league = Premier League</t>
         </is>
       </c>
       <c r="D23" s="6"/>
@@ -956,18 +957,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_183</t>
+          <t xml:space="preserve">simple_python_229</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search for current lawsuits filed against Apple in Santa Clara County.</t>
+          <t xml:space="preserve">What's my Big Five Personality trait scores given that I am efficient, organized, easy going and compassionate?</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">entity = Apple
-county = Santa Clara County</t>
+          <t xml:space="preserve">characteristics = efficient, organized, easy going, compassionate</t>
         </is>
       </c>
       <c r="D24" s="6"/>
@@ -979,17 +979,19 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_138</t>
+          <t xml:space="preserve">multiple_135</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How to obtain the detailed case information of the R vs Adams legal case?</t>
+          <t xml:space="preserve">Who was the victim in the case docket numbered 2022/AL2562 in California?</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">case_id = R vs Adams</t>
+          <t xml:space="preserve">docket = 2022/AL2562
+court = California
+info_type = victim</t>
         </is>
       </c>
       <c r="D25" s="6"/>
@@ -1001,18 +1003,19 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_177</t>
+          <t xml:space="preserve">simple_python_281</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find all Patent lawsuit cases of Facebook in 2018.</t>
+          <t xml:space="preserve">Find the details about the musical instrument 'Violin' from 'Stradivarius' maker, made in the year 1721.</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">company_name = Facebook
-year = 2018</t>
+          <t xml:space="preserve">name = Violin
+maker = Stradivarius
+year = 1721</t>
         </is>
       </c>
       <c r="D26" s="6"/>
@@ -1024,18 +1027,18 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_144</t>
+          <t xml:space="preserve">simple_python_236</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the air quality index in London 2022/08/16?</t>
+          <t xml:space="preserve">Get start date on the American Civil War.</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = London
-date = 2022/08/16</t>
+          <t xml:space="preserve">event_name = American Civil War
+specific_info = start date</t>
         </is>
       </c>
       <c r="D27" s="6"/>
@@ -1047,18 +1050,18 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_325</t>
+          <t xml:space="preserve">multiple_83</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who won the last match between Chicago Bulls and Los Angeles Lakers?</t>
+          <t xml:space="preserve">How many goals has Lionel Messi scored for Barcelona till date?</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team1 = Chicago Bulls
-team2 = Los Angeles Lakers</t>
+          <t xml:space="preserve">player_name = Lionel Messi
+team_name = Barcelona</t>
         </is>
       </c>
       <c r="D28" s="6"/>
@@ -1070,20 +1073,19 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_385</t>
+          <t xml:space="preserve">simple_python_376</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book a hotel room with king size bed in Los Angeles for 2 nights starting from 15th October,2023.</t>
+          <t xml:space="preserve">What time is it currently in London, UK in 24 hour format?</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Los Angeles
-room_type = king size
-check_in_date = 15th October
-no_of_nights = 2</t>
+          <t xml:space="preserve">city = London
+country = UK
+display_format = 24 hour</t>
         </is>
       </c>
       <c r="D29" s="6"/>
@@ -1095,18 +1097,18 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_44</t>
+          <t xml:space="preserve">multiple_86</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How much will I weigh on Mars if my weight on Earth is 70 kg?</t>
+          <t xml:space="preserve">What are some recommended board games for 2 players and strategy based from store BoardGameGeek?</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight_earth_kg = 70
-planet = Mars</t>
+          <t xml:space="preserve">numPlayers = 2
+category = strategy</t>
         </is>
       </c>
       <c r="D30" s="6"/>
@@ -1118,18 +1120,18 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_63</t>
+          <t xml:space="preserve">simple_python_256</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find out how genetically similar a human and a chimp are in percentage.</t>
+          <t xml:space="preserve">Generate an image of a circle with a radius of 50 pixels and color 'Red'.</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">species1 = human
-species2 = chimp</t>
+          <t xml:space="preserve">radius = 50
+color = Red</t>
         </is>
       </c>
       <c r="D31" s="6"/>
@@ -1141,19 +1143,19 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_176</t>
+          <t xml:space="preserve">multiple_139</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give me the schedule of Manchester United for the next 6 games in Premier League.</t>
+          <t xml:space="preserve">Find details of patent lawsuits involving the company 'Apple Inc.' from the year 2010.</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_name = Manchester United
-num_of_games = 6
-league = Premier League</t>
+          <t xml:space="preserve">company_name = Apple Inc.
+year = 2010
+case_type = patent</t>
         </is>
       </c>
       <c r="D32" s="6"/>
@@ -1165,17 +1167,18 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_229</t>
+          <t xml:space="preserve">simple_python_210</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's my Big Five Personality trait scores given that I am efficient, organized, easy going and compassionate?</t>
+          <t xml:space="preserve">Get 5 latest news on Bitcoin in US</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">characteristics = efficient, organized, easy going, compassionate</t>
+          <t xml:space="preserve">topic = Bitcoin
+quantity = 5</t>
         </is>
       </c>
       <c r="D33" s="6"/>
@@ -1187,19 +1190,17 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_135</t>
+          <t xml:space="preserve">simple_python_248</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who was the victim in the case docket numbered 2022/AL2562 in California?</t>
+          <t xml:space="preserve">Who invented the theory of relativity and in which year?</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">docket = 2022/AL2562
-court = California
-info_type = victim</t>
+          <t xml:space="preserve">invention_name = theory of relativity</t>
         </is>
       </c>
       <c r="D34" s="6"/>
@@ -1211,19 +1212,19 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_281</t>
+          <t xml:space="preserve">multiple_146</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the details about the musical instrument 'Violin' from 'Stradivarius' maker, made in the year 1721.</t>
+          <t xml:space="preserve">Find restaurants near me within 10 miles that offer Chinese cuisine in Seattle.</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">name = Violin
-maker = Stradivarius
-year = 1721</t>
+          <t xml:space="preserve">location = Seattle
+cuisine = Chinese
+max_distance = 10</t>
         </is>
       </c>
       <c r="D35" s="6"/>
@@ -1235,18 +1236,19 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_236</t>
+          <t xml:space="preserve">simple_python_361</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get start date on the American Civil War.</t>
+          <t xml:space="preserve">Find Italian restaurants near New York city that serves gluten-free options.</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_name = American Civil War
-specific_info = start date</t>
+          <t xml:space="preserve">city = New York city
+cuisine = Italian
+diet = gluten-free</t>
         </is>
       </c>
       <c r="D36" s="6"/>
@@ -1258,18 +1260,17 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_83</t>
+          <t xml:space="preserve">multiple_181</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many goals has Lionel Messi scored for Barcelona till date?</t>
+          <t xml:space="preserve">Get me the details of the last game played by Liverpool F.C. Include its statistics.</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">player_name = Lionel Messi
-team_name = Barcelona</t>
+          <t xml:space="preserve">team_name = Liverpool F.C.</t>
         </is>
       </c>
       <c r="D37" s="6"/>
@@ -1281,19 +1282,18 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_376</t>
+          <t xml:space="preserve">simple_python_330</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What time is it currently in London, UK in 24 hour format?</t>
+          <t xml:space="preserve">What's the average review rating and the age range for the board game 'Catan'?</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">city = London
-country = UK
-display_format = 24 hour</t>
+          <t xml:space="preserve">game_name = Catan
+info_required = average review rating, age range</t>
         </is>
       </c>
       <c r="D38" s="6"/>
@@ -1305,18 +1305,17 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_86</t>
+          <t xml:space="preserve">simple_python_149</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are some recommended board games for 2 players and strategy based from store BoardGameGeek?</t>
+          <t xml:space="preserve">What's the current stock price of Apple and Microsoft?</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">numPlayers = 2
-category = strategy</t>
+          <t xml:space="preserve">company_names = Apple, Microsoft</t>
         </is>
       </c>
       <c r="D39" s="6"/>
@@ -1328,18 +1327,19 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_256</t>
+          <t xml:space="preserve">multiple_17</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate an image of a circle with a radius of 50 pixels and color 'Red'.</t>
+          <t xml:space="preserve">Find the conversion rate from Euro to Dollar at January 1, 2022</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">radius = 50
-color = Red</t>
+          <t xml:space="preserve">from_currency = Euro
+to_currency = Dollar
+date = January 1, 2022</t>
         </is>
       </c>
       <c r="D40" s="6"/>
@@ -1351,19 +1351,18 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_139</t>
+          <t xml:space="preserve">simple_python_253</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find details of patent lawsuits involving the company 'Apple Inc.' from the year 2010.</t>
+          <t xml:space="preserve">Retrieve the full historyof Buddhism</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">company_name = Apple Inc.
-year = 2010
-case_type = patent</t>
+          <t xml:space="preserve">religion_name = Buddhism
+detail_level = full</t>
         </is>
       </c>
       <c r="D41" s="6"/>
@@ -1375,18 +1374,19 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_68</t>
+          <t xml:space="preserve">multiple_90</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predict the growth of forest in Yellowstone National Park for the next 5 years including human impact.</t>
+          <t xml:space="preserve">I want a seafood restaurant in Seattle that can accommodate a group of 5.</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Yellowstone National Park
-years = 5</t>
+          <t xml:space="preserve">location = Seattle
+cuisine = seafood
+group_size = 5</t>
         </is>
       </c>
       <c r="D42" s="6"/>
